--- a/src/test/java/gbench/webapps/crawler/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/crawler/api/model/data/datafile.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\world\api\model\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\crawler\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA48A41-CCA9-4F74-8119-4416825C3E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF1D433-A4BE-4564-8C51-7C3C08B58EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="316">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -878,7 +878,220 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>具体事物，不占用空间</t>
+    <t>连词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>而</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并列关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为：和、又，或不译</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为：就、才、接着、然后。表承接关系的前后两件事，逻辑上联系比较紧密，时间上有先后关系。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）蟹六跪而二螯（《劝学》）
+2）永州之野产异蛇，黑质而白章。（《捕蛇者说》）
+3）秦强而赵弱（《廉颇蔺相如列传》）
+4）此不为远者小而近者大乎？（《两小儿辩日》）
+5）因左手把秦王之袖，而右手持匕首揕之（《荆轲刺秦王》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）郑人有欲买履者，先自度其足，而置之其坐（《韩非子》）
+2）余闻而愈悲（《狱中杂记》）
+3）（秦）灭滑而还（《崤之战》）
+4）图穷而匕首见（《荆轲刺秦王》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>递进关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为：并且、而且，还。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转折关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为：却、但、可是、然而。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）君子博学而日参省乎己（《师说》）
+2）学而时习之，不亦说乎？（《论语》）
+3）臣虽下愚，知其不可，而况于明哲乎（《谏太宗十思疏》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）青取之于蓝而青于蓝。《劝学》
+2）有如此之势，而为秦人积威之所劫（《六国论》）
+3）涂有饿莩而不知发（《孟子》）
+4）舍其锦绣，邻有短褐而欲窃之（《公输》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为：如果、假使。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表假设关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因果关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承接/顺成关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为：因而、所以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（间隔修饰语与被修饰语，即间隔状语和中心词，也可称偏正关系），可译为：地、着、来，或不译。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）吾尝终日而思矣，不如须臾之所学也（《劝学》）
+2）河曲智叟笑而止之曰（《愚公移山》）
+3）子路率尔而对（《论语》）
+4）呼尔而与之，行道之人弗受；蹴尔而与之，乞人不屑也。（《孟子》）
+5）民之从事，常于几成而败之（《老子》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目的关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译作：为了、来、以便，也可保留而，或不译。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）缦立远视，而望幸焉（《阿房宫赋》）
+2）籍吏民，封府库，而待将军（《鸿门宴》）
+3）君岂有升斗之水而活我哉？（《庄子》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二人称代词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为：你（们）、你（们）的。中学教材有时说而通尔。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）妪每谓予曰：其所，而母立于兹。（《项脊轩志》）
+2）而翁归，自与汝复算耳！（《促织》）
+3）早缫而绪，早织而缕，字而幼孩，遂而鸡豚（《种树郭橐驼传》）
+4）而翁长铨，迁我京职，则汝朝夕侍母（《记王忠肃公翱三事》）
+5）滔滔者天下皆是也，而谁以易之？（《论语》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用作比况动词，译为如同、好像。它与如是同源字，在上古时读音相近，意义相通。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比况动词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>溺死者千有余人，军惊而坏都舍（《察今》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXAMPLES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何/曷/盍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑问代词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单独作谓语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后面常有语气助词哉也等，可译为为什么（呢）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）何者？严大国之威以修敬也（《廉颇蔺相如列传》）
+2）予尝求古仁人之心，或异二者之为，何哉？（《岳阳楼记》）
+3）邻国之民不加少，寡人之民不加多，何也？（《孟子》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动词或介词宾语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为哪里什么。在古汉语中，疑问代词宾语前置，翻译时，语序要调整。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）大王来何操？（《鸿门宴》）
+2）王见之曰：牛何之？（《孟子》）
+3）君何以知燕王？（《廉颇蔺相如列传》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作定语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可译为什么哪里。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）其间旦暮闻何物，杜鹃啼血猿哀鸣。（《琵琶行》）
+2）然则何时而乐耶？（《岳阳楼记》）
+3）丞相祠堂何处寻？（《蜀相》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）诸君而有意，瞻予马首可也（《冯婉贞》）
+2）人而无信，不知其可也（《论语》）
+3）子产而死，谁其嗣之？（《左传》）
+4）死而有知，其几何离？（《祭十二郎文》）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）余亦悔其随之而不得极夫游之乐也（《游褒禅山记》）
+2）有圣人作，构木为巢，以避群害，而民悦之，使王天下（《韩非子》）
+3）其人居远未来，而为留待（《荆轲刺秦王》）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -886,7 +1099,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -909,16 +1122,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -926,14 +1168,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5840,152 +6115,440 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBFA0B0-09A3-4E87-9D3C-50BFACFA9A69}">
-  <dimension ref="B2:F9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:G22"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="55.125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="7" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3">
+      <c r="G2" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="4">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="4">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="60" x14ac:dyDescent="0.2">
+      <c r="B10" s="4">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>264</v>
-      </c>
-      <c r="D4" t="s">
-        <v>259</v>
-      </c>
-      <c r="E4" t="s">
-        <v>262</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E10" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="B11" s="4">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D5" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E11" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="B12" s="4">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E12" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="B13" s="4">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E7" t="s">
-        <v>262</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E13" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="B14" s="4">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" t="s">
-        <v>262</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E14" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="B15" s="4">
+        <v>13</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E15" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="60" x14ac:dyDescent="0.2">
+      <c r="B16" s="4">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>270</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="B17" s="4">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="60" x14ac:dyDescent="0.2">
+      <c r="B18" s="4">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="24" x14ac:dyDescent="0.2">
+      <c r="B19" s="4">
+        <v>17</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="B20" s="4">
+        <v>18</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="B21" s="4">
+        <v>19</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="36" x14ac:dyDescent="0.2">
+      <c r="B22" s="4">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>